--- a/Generate Files/BOM/243-4xx-Suiveur-IR-7.xlsx
+++ b/Generate Files/BOM/243-4xx-Suiveur-IR-7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/243-436-Dev-Prod4-Certifications/Projet de fin de session/243-436-PCB-SuiveurDeLigne-7capteurs/Generate Files/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{ED19AEE6-1918-4208-926C-4A584F112D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97BFF6EC-6A5F-4407-8451-703427C9D41F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4D54C1C-C09B-4676-83E6-4C95A131CFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="20112" windowHeight="11904" xr2:uid="{44F830C7-CCF7-4EA0-89FC-3E34DE0E31B0}"/>
+    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8880" xr2:uid="{720A5560-D0B1-4F77-A21D-D45AC179371F}"/>
   </bookViews>
   <sheets>
     <sheet name="243-4xx-Suiveur-IR-7" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="100">
   <si>
     <t>LibRef</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>CEGEP</t>
+  </si>
+  <si>
     <t>Code CEGEP</t>
   </si>
   <si>
@@ -239,19 +242,19 @@
     <t>C100001</t>
   </si>
   <si>
-    <t>RES031</t>
-  </si>
-  <si>
-    <t>Res 150R 1% 0805</t>
+    <t>RES042</t>
+  </si>
+  <si>
+    <t>Res 150R 5% 1206</t>
   </si>
   <si>
     <t>R8, R9, R10, R11, R12, R13, R14</t>
   </si>
   <si>
-    <t>RC0805FR-07150RL</t>
-  </si>
-  <si>
-    <t>C114523</t>
+    <t>RESI0045SMT</t>
+  </si>
+  <si>
+    <t>AV-P24--R14-J04</t>
   </si>
   <si>
     <t>RES008</t>
@@ -326,7 +329,7 @@
     <t>KIC8574SM</t>
   </si>
   <si>
-    <t xml:space="preserve">R13-D030  </t>
+    <t>R13-D030</t>
   </si>
   <si>
     <t>HG Semi</t>
@@ -731,8 +734,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C67055-2395-4267-8DC6-F481C2C08570}">
-  <dimension ref="A1:N12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3931E7B6-1D73-41C2-93B2-F683423800A1}">
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.21875" customWidth="1"/>
@@ -740,13 +743,13 @@
     <col min="3" max="3" width="12.5546875" customWidth="1"/>
     <col min="4" max="4" width="32.33203125" customWidth="1"/>
     <col min="5" max="5" width="34.33203125" customWidth="1"/>
-    <col min="6" max="9" width="16.33203125" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="11" width="28.77734375" customWidth="1"/>
-    <col min="12" max="14" width="16.33203125" customWidth="1"/>
+    <col min="6" max="10" width="16.33203125" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" customWidth="1"/>
+    <col min="12" max="12" width="28.77734375" customWidth="1"/>
+    <col min="13" max="15" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -789,30 +792,31 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="H2" s="1"/>
       <c r="I2" s="2" t="s">
         <v>20</v>
       </c>
@@ -822,69 +826,71 @@
       <c r="K2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="1"/>
+      <c r="L2" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="M2" s="1"/>
-      <c r="N2" s="2" t="s">
-        <v>23</v>
+      <c r="N2" s="1"/>
+      <c r="O2" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1">
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="H3" s="1"/>
       <c r="I3" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="M3" s="1"/>
-      <c r="N3" s="2" t="s">
-        <v>23</v>
+      <c r="N3" s="1"/>
+      <c r="O3" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
@@ -892,13 +898,13 @@
         <v>37</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>39</v>
@@ -907,28 +913,29 @@
         <v>40</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="2" t="s">
         <v>46</v>
       </c>
@@ -939,168 +946,168 @@
         <v>48</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="O5" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1">
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="F6" s="1"/>
       <c r="G6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>23</v>
+        <v>60</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1">
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="H7" s="1"/>
       <c r="I7" s="2" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="M7" s="1"/>
-      <c r="N7" s="2" t="s">
-        <v>23</v>
+      <c r="N7" s="1"/>
+      <c r="O7" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="H8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>70</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="2" t="s">
-        <v>23</v>
+      <c r="N8" s="1"/>
+      <c r="O8" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="2" t="s">
-        <v>28</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9" s="1"/>
       <c r="I9" s="2" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>77</v>
@@ -1109,108 +1116,111 @@
         <v>78</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" s="1">
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="H10" s="1"/>
       <c r="I10" s="2" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L10" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="M10" s="1"/>
-      <c r="N10" s="2" t="s">
-        <v>23</v>
+      <c r="N10" s="1"/>
+      <c r="O10" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1">
         <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="K11" s="2" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>23</v>
+        <v>90</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F12" s="2" t="s">
         <v>94</v>
       </c>
+      <c r="F12" s="1"/>
       <c r="G12" s="2" t="s">
         <v>95</v>
       </c>
@@ -1218,22 +1228,25 @@
         <v>96</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>23</v>
+        <v>99</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
